--- a/data/tasa_eur.xlsx
+++ b/data/tasa_eur.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E01E287B-3755-415D-A1A7-31297A4D5F27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76ED5C75-BC9F-4031-841C-DEAA5C181BFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6540" uniqueCount="6495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6553" uniqueCount="6508">
   <si>
     <t>Fecha</t>
   </si>
@@ -19473,10 +19473,49 @@
     <t>2026/07/23</t>
   </si>
   <si>
+    <t>2026/07/24</t>
+  </si>
+  <si>
+    <t>2026/07/25</t>
+  </si>
+  <si>
+    <t>2026/07/26</t>
+  </si>
+  <si>
+    <t>2026/07/27</t>
+  </si>
+  <si>
+    <t>2026/07/28</t>
+  </si>
+  <si>
+    <t>2026/07/29</t>
+  </si>
+  <si>
+    <t>2026/07/30</t>
+  </si>
+  <si>
+    <t>2026/07/31</t>
+  </si>
+  <si>
+    <t>2026/08/01</t>
+  </si>
+  <si>
+    <t>2026/08/02</t>
+  </si>
+  <si>
+    <t>2026/08/03</t>
+  </si>
+  <si>
+    <t>2026/08/04</t>
+  </si>
+  <si>
+    <t>2026/08/05</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Descargado de sistema del Banco de la República viernes, 24 de julio de 2026 8:07:14 a. m.</t>
+    <t>Descargado de sistema del Banco de la República jueves, 6 de agosto de 2026 8:19:24 a. m.</t>
   </si>
   <si>
     <t>Nombre de la serie</t>
@@ -19892,7 +19931,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B6458"/>
+  <dimension ref="A1:B6471"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="20.109375" customWidth="1"/>
@@ -71542,15 +71581,119 @@
       <c r="A6456" t="s">
         <v>6485</v>
       </c>
+      <c r="B6456" s="1">
+        <v>3663.2528400000001</v>
+      </c>
     </row>
     <row r="6457" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6457" t="s">
-        <v>6485</v>
+        <v>6486</v>
+      </c>
+      <c r="B6457" s="1">
+        <v>3653.2962200000002</v>
       </c>
     </row>
     <row r="6458" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6458" t="s">
-        <v>6486</v>
+        <v>6487</v>
+      </c>
+      <c r="B6458" s="1">
+        <v>3653.2962200000002</v>
+      </c>
+    </row>
+    <row r="6459" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6459" t="s">
+        <v>6488</v>
+      </c>
+      <c r="B6459" s="1">
+        <v>3650.8883000000001</v>
+      </c>
+    </row>
+    <row r="6460" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6460" t="s">
+        <v>6489</v>
+      </c>
+      <c r="B6460" s="1">
+        <v>3650.1238800000001</v>
+      </c>
+    </row>
+    <row r="6461" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6461" t="s">
+        <v>6490</v>
+      </c>
+      <c r="B6461" s="1">
+        <v>3648.7609400000001</v>
+      </c>
+    </row>
+    <row r="6462" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6462" t="s">
+        <v>6491</v>
+      </c>
+      <c r="B6462" s="1">
+        <v>3688.2291599999999</v>
+      </c>
+    </row>
+    <row r="6463" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6463" t="s">
+        <v>6492</v>
+      </c>
+      <c r="B6463" s="1">
+        <v>3604.0058300000001</v>
+      </c>
+    </row>
+    <row r="6464" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6464" t="s">
+        <v>6493</v>
+      </c>
+      <c r="B6464" s="1">
+        <v>3617.4902699999998</v>
+      </c>
+    </row>
+    <row r="6465" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6465" t="s">
+        <v>6494</v>
+      </c>
+      <c r="B6465" s="1">
+        <v>3617.4902699999998</v>
+      </c>
+    </row>
+    <row r="6466" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6466" t="s">
+        <v>6495</v>
+      </c>
+      <c r="B6466" s="1">
+        <v>3620.1627899999999</v>
+      </c>
+    </row>
+    <row r="6467" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6467" t="s">
+        <v>6496</v>
+      </c>
+      <c r="B6467" s="1">
+        <v>3722.59753</v>
+      </c>
+    </row>
+    <row r="6468" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6468" t="s">
+        <v>6497</v>
+      </c>
+      <c r="B6468" s="1">
+        <v>3702.1704</v>
+      </c>
+    </row>
+    <row r="6469" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6469" t="s">
+        <v>6498</v>
+      </c>
+    </row>
+    <row r="6470" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6470" t="s">
+        <v>6498</v>
+      </c>
+    </row>
+    <row r="6471" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6471" t="s">
+        <v>6499</v>
       </c>
     </row>
   </sheetData>
@@ -71573,19 +71716,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>6487</v>
+        <v>6500</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>6488</v>
+        <v>6501</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>6489</v>
+        <v>6502</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>6490</v>
+        <v>6503</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>6491</v>
+        <v>6504</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71596,13 +71739,13 @@
         <v>17</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>6492</v>
+        <v>6505</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>6493</v>
+        <v>6506</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>6494</v>
+        <v>6507</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71613,13 +71756,13 @@
         <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>6492</v>
+        <v>6505</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>6493</v>
+        <v>6506</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>6494</v>
+        <v>6507</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71630,13 +71773,13 @@
         <v>19</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>6492</v>
+        <v>6505</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>6493</v>
+        <v>6506</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>6494</v>
+        <v>6507</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71647,13 +71790,13 @@
         <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>6492</v>
+        <v>6505</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>6493</v>
+        <v>6506</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>6494</v>
+        <v>6507</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71664,13 +71807,13 @@
         <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>6492</v>
+        <v>6505</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>6493</v>
+        <v>6506</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>6494</v>
+        <v>6507</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71681,13 +71824,13 @@
         <v>22</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>6492</v>
+        <v>6505</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>6493</v>
+        <v>6506</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>6494</v>
+        <v>6507</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71698,13 +71841,13 @@
         <v>23</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>6492</v>
+        <v>6505</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>6493</v>
+        <v>6506</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>6494</v>
+        <v>6507</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71715,13 +71858,13 @@
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>6492</v>
+        <v>6505</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>6493</v>
+        <v>6506</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>6494</v>
+        <v>6507</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71732,13 +71875,13 @@
         <v>25</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>6492</v>
+        <v>6505</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>6493</v>
+        <v>6506</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>6494</v>
+        <v>6507</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71749,13 +71892,13 @@
         <v>26</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>6492</v>
+        <v>6505</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>6493</v>
+        <v>6506</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>6494</v>
+        <v>6507</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71766,13 +71909,13 @@
         <v>27</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>6492</v>
+        <v>6505</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>6493</v>
+        <v>6506</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>6494</v>
+        <v>6507</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71783,13 +71926,13 @@
         <v>28</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>6492</v>
+        <v>6505</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>6493</v>
+        <v>6506</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>6494</v>
+        <v>6507</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71800,13 +71943,13 @@
         <v>29</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>6492</v>
+        <v>6505</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>6493</v>
+        <v>6506</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>6494</v>
+        <v>6507</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71817,13 +71960,13 @@
         <v>30</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>6492</v>
+        <v>6505</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>6493</v>
+        <v>6506</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>6494</v>
+        <v>6507</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71834,13 +71977,13 @@
         <v>31</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>6492</v>
+        <v>6505</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>6493</v>
+        <v>6506</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>6494</v>
+        <v>6507</v>
       </c>
     </row>
   </sheetData>

--- a/data/tasa_eur.xlsx
+++ b/data/tasa_eur.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76ED5C75-BC9F-4031-841C-DEAA5C181BFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{740FB969-3E40-427F-AF95-A6A745EE6827}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6553" uniqueCount="6508">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6559" uniqueCount="6514">
   <si>
     <t>Fecha</t>
   </si>
@@ -19512,10 +19512,28 @@
     <t>2026/08/05</t>
   </si>
   <si>
+    <t>2026/08/06</t>
+  </si>
+  <si>
+    <t>2026/08/07</t>
+  </si>
+  <si>
+    <t>2026/08/08</t>
+  </si>
+  <si>
+    <t>2026/08/09</t>
+  </si>
+  <si>
+    <t>2026/08/10</t>
+  </si>
+  <si>
+    <t>2026/08/11</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Descargado de sistema del Banco de la República jueves, 6 de agosto de 2026 8:19:24 a. m.</t>
+    <t>Descargado de sistema del Banco de la República miércoles, 12 de agosto de 2026 9:16:33 a. m.</t>
   </si>
   <si>
     <t>Nombre de la serie</t>
@@ -19931,7 +19949,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B6471"/>
+  <dimension ref="A1:B6477"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="20.109375" customWidth="1"/>
@@ -71685,15 +71703,63 @@
       <c r="A6469" t="s">
         <v>6498</v>
       </c>
+      <c r="B6469" s="1">
+        <v>3667.4378999999999</v>
+      </c>
     </row>
     <row r="6470" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6470" t="s">
-        <v>6498</v>
+        <v>6499</v>
+      </c>
+      <c r="B6470" s="1">
+        <v>3647.9367499999998</v>
       </c>
     </row>
     <row r="6471" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6471" t="s">
-        <v>6499</v>
+        <v>6500</v>
+      </c>
+      <c r="B6471" s="1">
+        <v>3647.9367499999998</v>
+      </c>
+    </row>
+    <row r="6472" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6472" t="s">
+        <v>6501</v>
+      </c>
+      <c r="B6472" s="1">
+        <v>3647.9367499999998</v>
+      </c>
+    </row>
+    <row r="6473" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6473" t="s">
+        <v>6502</v>
+      </c>
+      <c r="B6473" s="1">
+        <v>3647.1473900000001</v>
+      </c>
+    </row>
+    <row r="6474" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6474" t="s">
+        <v>6503</v>
+      </c>
+      <c r="B6474" s="1">
+        <v>3607.5737399999998</v>
+      </c>
+    </row>
+    <row r="6475" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6475" t="s">
+        <v>6504</v>
+      </c>
+    </row>
+    <row r="6476" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6476" t="s">
+        <v>6504</v>
+      </c>
+    </row>
+    <row r="6477" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6477" t="s">
+        <v>6505</v>
       </c>
     </row>
   </sheetData>
@@ -71716,19 +71782,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>6500</v>
+        <v>6506</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>6501</v>
+        <v>6507</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>6502</v>
+        <v>6508</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>6503</v>
+        <v>6509</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>6504</v>
+        <v>6510</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71739,13 +71805,13 @@
         <v>17</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>6505</v>
+        <v>6511</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>6506</v>
+        <v>6512</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>6507</v>
+        <v>6513</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71756,13 +71822,13 @@
         <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>6505</v>
+        <v>6511</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>6506</v>
+        <v>6512</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>6507</v>
+        <v>6513</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71773,13 +71839,13 @@
         <v>19</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>6505</v>
+        <v>6511</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>6506</v>
+        <v>6512</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>6507</v>
+        <v>6513</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71790,13 +71856,13 @@
         <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>6505</v>
+        <v>6511</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>6506</v>
+        <v>6512</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>6507</v>
+        <v>6513</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71807,13 +71873,13 @@
         <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>6505</v>
+        <v>6511</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>6506</v>
+        <v>6512</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>6507</v>
+        <v>6513</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71824,13 +71890,13 @@
         <v>22</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>6505</v>
+        <v>6511</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>6506</v>
+        <v>6512</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>6507</v>
+        <v>6513</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71841,13 +71907,13 @@
         <v>23</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>6505</v>
+        <v>6511</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>6506</v>
+        <v>6512</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>6507</v>
+        <v>6513</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71858,13 +71924,13 @@
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>6505</v>
+        <v>6511</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>6506</v>
+        <v>6512</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>6507</v>
+        <v>6513</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71875,13 +71941,13 @@
         <v>25</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>6505</v>
+        <v>6511</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>6506</v>
+        <v>6512</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>6507</v>
+        <v>6513</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71892,13 +71958,13 @@
         <v>26</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>6505</v>
+        <v>6511</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>6506</v>
+        <v>6512</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>6507</v>
+        <v>6513</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71909,13 +71975,13 @@
         <v>27</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>6505</v>
+        <v>6511</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>6506</v>
+        <v>6512</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>6507</v>
+        <v>6513</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71926,13 +71992,13 @@
         <v>28</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>6505</v>
+        <v>6511</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>6506</v>
+        <v>6512</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>6507</v>
+        <v>6513</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71943,13 +72009,13 @@
         <v>29</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>6505</v>
+        <v>6511</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>6506</v>
+        <v>6512</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>6507</v>
+        <v>6513</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71960,13 +72026,13 @@
         <v>30</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>6505</v>
+        <v>6511</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>6506</v>
+        <v>6512</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>6507</v>
+        <v>6513</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71977,13 +72043,13 @@
         <v>31</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>6505</v>
+        <v>6511</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>6506</v>
+        <v>6512</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>6507</v>
+        <v>6513</v>
       </c>
     </row>
   </sheetData>

--- a/data/tasa_eur.xlsx
+++ b/data/tasa_eur.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{740FB969-3E40-427F-AF95-A6A745EE6827}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E739CFF-5806-49F1-A6B5-433514C84C14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6559" uniqueCount="6514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6561" uniqueCount="6516">
   <si>
     <t>Fecha</t>
   </si>
@@ -19530,10 +19530,16 @@
     <t>2026/08/11</t>
   </si>
   <si>
+    <t>2026/08/12</t>
+  </si>
+  <si>
+    <t>2026/08/13</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Descargado de sistema del Banco de la República miércoles, 12 de agosto de 2026 9:16:33 a. m.</t>
+    <t>Descargado de sistema del Banco de la República viernes, 14 de agosto de 2026 11:01:55 a. m.</t>
   </si>
   <si>
     <t>Nombre de la serie</t>
@@ -19949,7 +19955,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B6477"/>
+  <dimension ref="A1:B6479"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="20.109375" customWidth="1"/>
@@ -71751,15 +71757,31 @@
       <c r="A6475" t="s">
         <v>6504</v>
       </c>
+      <c r="B6475" s="1">
+        <v>3602.3389900000002</v>
+      </c>
     </row>
     <row r="6476" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6476" t="s">
-        <v>6504</v>
+        <v>6505</v>
+      </c>
+      <c r="B6476" s="1">
+        <v>3605.6705900000002</v>
       </c>
     </row>
     <row r="6477" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6477" t="s">
-        <v>6505</v>
+        <v>6506</v>
+      </c>
+    </row>
+    <row r="6478" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6478" t="s">
+        <v>6506</v>
+      </c>
+    </row>
+    <row r="6479" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6479" t="s">
+        <v>6507</v>
       </c>
     </row>
   </sheetData>
@@ -71782,19 +71804,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>6506</v>
+        <v>6508</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>6507</v>
+        <v>6509</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>6508</v>
+        <v>6510</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>6509</v>
+        <v>6511</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>6510</v>
+        <v>6512</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71805,13 +71827,13 @@
         <v>17</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>6511</v>
+        <v>6513</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>6512</v>
+        <v>6514</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>6513</v>
+        <v>6515</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71822,13 +71844,13 @@
         <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>6511</v>
+        <v>6513</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>6512</v>
+        <v>6514</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>6513</v>
+        <v>6515</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71839,13 +71861,13 @@
         <v>19</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>6511</v>
+        <v>6513</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>6512</v>
+        <v>6514</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>6513</v>
+        <v>6515</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71856,13 +71878,13 @@
         <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>6511</v>
+        <v>6513</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>6512</v>
+        <v>6514</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>6513</v>
+        <v>6515</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71873,13 +71895,13 @@
         <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>6511</v>
+        <v>6513</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>6512</v>
+        <v>6514</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>6513</v>
+        <v>6515</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71890,13 +71912,13 @@
         <v>22</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>6511</v>
+        <v>6513</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>6512</v>
+        <v>6514</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>6513</v>
+        <v>6515</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71907,13 +71929,13 @@
         <v>23</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>6511</v>
+        <v>6513</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>6512</v>
+        <v>6514</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>6513</v>
+        <v>6515</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71924,13 +71946,13 @@
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>6511</v>
+        <v>6513</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>6512</v>
+        <v>6514</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>6513</v>
+        <v>6515</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71941,13 +71963,13 @@
         <v>25</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>6511</v>
+        <v>6513</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>6512</v>
+        <v>6514</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>6513</v>
+        <v>6515</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71958,13 +71980,13 @@
         <v>26</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>6511</v>
+        <v>6513</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>6512</v>
+        <v>6514</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>6513</v>
+        <v>6515</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71975,13 +71997,13 @@
         <v>27</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>6511</v>
+        <v>6513</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>6512</v>
+        <v>6514</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>6513</v>
+        <v>6515</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71992,13 +72014,13 @@
         <v>28</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>6511</v>
+        <v>6513</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>6512</v>
+        <v>6514</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>6513</v>
+        <v>6515</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -72009,13 +72031,13 @@
         <v>29</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>6511</v>
+        <v>6513</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>6512</v>
+        <v>6514</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>6513</v>
+        <v>6515</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -72026,13 +72048,13 @@
         <v>30</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>6511</v>
+        <v>6513</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>6512</v>
+        <v>6514</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>6513</v>
+        <v>6515</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -72043,13 +72065,13 @@
         <v>31</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>6511</v>
+        <v>6513</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>6512</v>
+        <v>6514</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>6513</v>
+        <v>6515</v>
       </c>
     </row>
   </sheetData>

--- a/data/tasa_eur.xlsx
+++ b/data/tasa_eur.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E739CFF-5806-49F1-A6B5-433514C84C14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{285B49D3-2A71-4D73-A22D-247383D8DB4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6561" uniqueCount="6516">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6568" uniqueCount="6523">
   <si>
     <t>Fecha</t>
   </si>
@@ -19536,10 +19536,31 @@
     <t>2026/08/13</t>
   </si>
   <si>
+    <t>2026/08/14</t>
+  </si>
+  <si>
+    <t>2026/08/15</t>
+  </si>
+  <si>
+    <t>2026/08/16</t>
+  </si>
+  <si>
+    <t>2026/08/17</t>
+  </si>
+  <si>
+    <t>2026/08/18</t>
+  </si>
+  <si>
+    <t>2026/08/19</t>
+  </si>
+  <si>
+    <t>2026/08/20</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Descargado de sistema del Banco de la República viernes, 14 de agosto de 2026 11:01:55 a. m.</t>
+    <t>Descargado de sistema del Banco de la República viernes, 21 de agosto de 2026 8:52:50 a. m.</t>
   </si>
   <si>
     <t>Nombre de la serie</t>
@@ -19955,7 +19976,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B6479"/>
+  <dimension ref="A1:B6486"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="20.109375" customWidth="1"/>
@@ -71773,15 +71794,71 @@
       <c r="A6477" t="s">
         <v>6506</v>
       </c>
+      <c r="B6477" s="1">
+        <v>3621.9693299999999</v>
+      </c>
     </row>
     <row r="6478" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6478" t="s">
-        <v>6506</v>
+        <v>6507</v>
+      </c>
+      <c r="B6478" s="1">
+        <v>3623.2895600000002</v>
       </c>
     </row>
     <row r="6479" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6479" t="s">
-        <v>6507</v>
+        <v>6508</v>
+      </c>
+      <c r="B6479" s="1">
+        <v>3623.2895600000002</v>
+      </c>
+    </row>
+    <row r="6480" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6480" t="s">
+        <v>6509</v>
+      </c>
+      <c r="B6480" s="1">
+        <v>3625.1667499999999</v>
+      </c>
+    </row>
+    <row r="6481" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6481" t="s">
+        <v>6510</v>
+      </c>
+      <c r="B6481" s="1">
+        <v>3623.6024299999999</v>
+      </c>
+    </row>
+    <row r="6482" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6482" t="s">
+        <v>6511</v>
+      </c>
+      <c r="B6482" s="1">
+        <v>3614.11877</v>
+      </c>
+    </row>
+    <row r="6483" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6483" t="s">
+        <v>6512</v>
+      </c>
+      <c r="B6483" s="1">
+        <v>3567.5333500000002</v>
+      </c>
+    </row>
+    <row r="6484" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6484" t="s">
+        <v>6513</v>
+      </c>
+    </row>
+    <row r="6485" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6485" t="s">
+        <v>6513</v>
+      </c>
+    </row>
+    <row r="6486" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6486" t="s">
+        <v>6514</v>
       </c>
     </row>
   </sheetData>
@@ -71804,19 +71881,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>6508</v>
+        <v>6515</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>6509</v>
+        <v>6516</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>6510</v>
+        <v>6517</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>6511</v>
+        <v>6518</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>6512</v>
+        <v>6519</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71827,13 +71904,13 @@
         <v>17</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>6513</v>
+        <v>6520</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>6514</v>
+        <v>6521</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>6515</v>
+        <v>6522</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71844,13 +71921,13 @@
         <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>6513</v>
+        <v>6520</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>6514</v>
+        <v>6521</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>6515</v>
+        <v>6522</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71861,13 +71938,13 @@
         <v>19</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>6513</v>
+        <v>6520</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>6514</v>
+        <v>6521</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>6515</v>
+        <v>6522</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71878,13 +71955,13 @@
         <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>6513</v>
+        <v>6520</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>6514</v>
+        <v>6521</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>6515</v>
+        <v>6522</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71895,13 +71972,13 @@
         <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>6513</v>
+        <v>6520</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>6514</v>
+        <v>6521</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>6515</v>
+        <v>6522</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71912,13 +71989,13 @@
         <v>22</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>6513</v>
+        <v>6520</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>6514</v>
+        <v>6521</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>6515</v>
+        <v>6522</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71929,13 +72006,13 @@
         <v>23</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>6513</v>
+        <v>6520</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>6514</v>
+        <v>6521</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>6515</v>
+        <v>6522</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71946,13 +72023,13 @@
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>6513</v>
+        <v>6520</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>6514</v>
+        <v>6521</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>6515</v>
+        <v>6522</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71963,13 +72040,13 @@
         <v>25</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>6513</v>
+        <v>6520</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>6514</v>
+        <v>6521</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>6515</v>
+        <v>6522</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71980,13 +72057,13 @@
         <v>26</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>6513</v>
+        <v>6520</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>6514</v>
+        <v>6521</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>6515</v>
+        <v>6522</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71997,13 +72074,13 @@
         <v>27</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>6513</v>
+        <v>6520</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>6514</v>
+        <v>6521</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>6515</v>
+        <v>6522</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -72014,13 +72091,13 @@
         <v>28</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>6513</v>
+        <v>6520</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>6514</v>
+        <v>6521</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>6515</v>
+        <v>6522</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -72031,13 +72108,13 @@
         <v>29</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>6513</v>
+        <v>6520</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>6514</v>
+        <v>6521</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>6515</v>
+        <v>6522</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -72048,13 +72125,13 @@
         <v>30</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>6513</v>
+        <v>6520</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>6514</v>
+        <v>6521</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>6515</v>
+        <v>6522</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -72065,13 +72142,13 @@
         <v>31</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>6513</v>
+        <v>6520</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>6514</v>
+        <v>6521</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>6515</v>
+        <v>6522</v>
       </c>
     </row>
   </sheetData>

--- a/data/tasa_eur.xlsx
+++ b/data/tasa_eur.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{285B49D3-2A71-4D73-A22D-247383D8DB4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5635EC3A-3040-49D7-A472-296D0823F531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6568" uniqueCount="6523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6579" uniqueCount="6534">
   <si>
     <t>Fecha</t>
   </si>
@@ -19557,10 +19557,43 @@
     <t>2026/08/20</t>
   </si>
   <si>
+    <t>2026/08/21</t>
+  </si>
+  <si>
+    <t>2026/08/22</t>
+  </si>
+  <si>
+    <t>2026/08/23</t>
+  </si>
+  <si>
+    <t>2026/08/24</t>
+  </si>
+  <si>
+    <t>2026/08/25</t>
+  </si>
+  <si>
+    <t>2026/08/26</t>
+  </si>
+  <si>
+    <t>2026/08/27</t>
+  </si>
+  <si>
+    <t>2026/08/28</t>
+  </si>
+  <si>
+    <t>2026/08/29</t>
+  </si>
+  <si>
+    <t>2026/08/30</t>
+  </si>
+  <si>
+    <t>2026/08/31</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Descargado de sistema del Banco de la República viernes, 21 de agosto de 2026 8:52:50 a. m.</t>
+    <t>Descargado de sistema del Banco de la República martes, 1 de septiembre de 2026 8:13:38 a. m.</t>
   </si>
   <si>
     <t>Nombre de la serie</t>
@@ -19976,7 +20009,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B6486"/>
+  <dimension ref="A1:B6497"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="20.109375" customWidth="1"/>
@@ -71850,15 +71883,103 @@
       <c r="A6484" t="s">
         <v>6513</v>
       </c>
+      <c r="B6484" s="1">
+        <v>3575.3932</v>
+      </c>
     </row>
     <row r="6485" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6485" t="s">
-        <v>6513</v>
+        <v>6514</v>
+      </c>
+      <c r="B6485" s="1">
+        <v>3558.0704700000001</v>
       </c>
     </row>
     <row r="6486" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6486" t="s">
-        <v>6514</v>
+        <v>6515</v>
+      </c>
+      <c r="B6486" s="1">
+        <v>3558.0704700000001</v>
+      </c>
+    </row>
+    <row r="6487" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6487" t="s">
+        <v>6516</v>
+      </c>
+      <c r="B6487" s="1">
+        <v>3555.9367900000002</v>
+      </c>
+    </row>
+    <row r="6488" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6488" t="s">
+        <v>6517</v>
+      </c>
+      <c r="B6488" s="1">
+        <v>3566.7943399999999</v>
+      </c>
+    </row>
+    <row r="6489" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6489" t="s">
+        <v>6518</v>
+      </c>
+      <c r="B6489" s="1">
+        <v>3588.7587899999999</v>
+      </c>
+    </row>
+    <row r="6490" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6490" t="s">
+        <v>6519</v>
+      </c>
+      <c r="B6490" s="1">
+        <v>3631.5023000000001</v>
+      </c>
+    </row>
+    <row r="6491" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6491" t="s">
+        <v>6520</v>
+      </c>
+      <c r="B6491" s="1">
+        <v>3653.9677799999999</v>
+      </c>
+    </row>
+    <row r="6492" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6492" t="s">
+        <v>6521</v>
+      </c>
+      <c r="B6492" s="1">
+        <v>3721.96225</v>
+      </c>
+    </row>
+    <row r="6493" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6493" t="s">
+        <v>6522</v>
+      </c>
+      <c r="B6493" s="1">
+        <v>3721.96225</v>
+      </c>
+    </row>
+    <row r="6494" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6494" t="s">
+        <v>6523</v>
+      </c>
+      <c r="B6494" s="1">
+        <v>3720.3608599999998</v>
+      </c>
+    </row>
+    <row r="6495" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6495" t="s">
+        <v>6524</v>
+      </c>
+    </row>
+    <row r="6496" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6496" t="s">
+        <v>6524</v>
+      </c>
+    </row>
+    <row r="6497" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6497" t="s">
+        <v>6525</v>
       </c>
     </row>
   </sheetData>
@@ -71881,19 +72002,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>6515</v>
+        <v>6526</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>6516</v>
+        <v>6527</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>6517</v>
+        <v>6528</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>6518</v>
+        <v>6529</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>6519</v>
+        <v>6530</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71904,13 +72025,13 @@
         <v>17</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>6520</v>
+        <v>6531</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>6521</v>
+        <v>6532</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>6522</v>
+        <v>6533</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71921,13 +72042,13 @@
         <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>6520</v>
+        <v>6531</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>6521</v>
+        <v>6532</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>6522</v>
+        <v>6533</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71938,13 +72059,13 @@
         <v>19</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>6520</v>
+        <v>6531</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>6521</v>
+        <v>6532</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>6522</v>
+        <v>6533</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71955,13 +72076,13 @@
         <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>6520</v>
+        <v>6531</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>6521</v>
+        <v>6532</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>6522</v>
+        <v>6533</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71972,13 +72093,13 @@
         <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>6520</v>
+        <v>6531</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>6521</v>
+        <v>6532</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>6522</v>
+        <v>6533</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -71989,13 +72110,13 @@
         <v>22</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>6520</v>
+        <v>6531</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>6521</v>
+        <v>6532</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>6522</v>
+        <v>6533</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -72006,13 +72127,13 @@
         <v>23</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>6520</v>
+        <v>6531</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>6521</v>
+        <v>6532</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>6522</v>
+        <v>6533</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -72023,13 +72144,13 @@
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>6520</v>
+        <v>6531</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>6521</v>
+        <v>6532</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>6522</v>
+        <v>6533</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -72040,13 +72161,13 @@
         <v>25</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>6520</v>
+        <v>6531</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>6521</v>
+        <v>6532</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>6522</v>
+        <v>6533</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -72057,13 +72178,13 @@
         <v>26</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>6520</v>
+        <v>6531</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>6521</v>
+        <v>6532</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>6522</v>
+        <v>6533</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -72074,13 +72195,13 @@
         <v>27</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>6520</v>
+        <v>6531</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>6521</v>
+        <v>6532</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>6522</v>
+        <v>6533</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -72091,13 +72212,13 @@
         <v>28</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>6520</v>
+        <v>6531</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>6521</v>
+        <v>6532</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>6522</v>
+        <v>6533</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -72108,13 +72229,13 @@
         <v>29</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>6520</v>
+        <v>6531</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>6521</v>
+        <v>6532</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>6522</v>
+        <v>6533</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -72125,13 +72246,13 @@
         <v>30</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>6520</v>
+        <v>6531</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>6521</v>
+        <v>6532</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>6522</v>
+        <v>6533</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -72142,13 +72263,13 @@
         <v>31</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>6520</v>
+        <v>6531</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>6521</v>
+        <v>6532</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>6522</v>
+        <v>6533</v>
       </c>
     </row>
   </sheetData>

--- a/data/tasa_eur.xlsx
+++ b/data/tasa_eur.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6540"/>
+  <dimension ref="A1:B6543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65821,6 +65821,36 @@
         <v>3572.45615</v>
       </c>
     </row>
+    <row r="6541">
+      <c r="A6541" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B6541" s="1" t="n">
+        <v>3572.45615</v>
+      </c>
+    </row>
+    <row r="6542">
+      <c r="A6542" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B6542" s="1" t="n">
+        <v>3561.02733</v>
+      </c>
+    </row>
+    <row r="6543">
+      <c r="A6543" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B6543" s="1" t="n">
+        <v>3549.43965</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/tasa_eur.xlsx
+++ b/data/tasa_eur.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6543"/>
+  <dimension ref="A1:B6552"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65851,6 +65851,96 @@
         <v>3549.43965</v>
       </c>
     </row>
+    <row r="6544">
+      <c r="A6544" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B6544" s="1" t="n">
+        <v>3551.00422</v>
+      </c>
+    </row>
+    <row r="6545">
+      <c r="A6545" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B6545" s="1" t="n">
+        <v>3573.64853</v>
+      </c>
+    </row>
+    <row r="6546">
+      <c r="A6546" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B6546" s="1" t="n">
+        <v>3568.4852</v>
+      </c>
+    </row>
+    <row r="6547">
+      <c r="A6547" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B6547" s="1" t="n">
+        <v>3538.70497</v>
+      </c>
+    </row>
+    <row r="6548">
+      <c r="A6548" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B6548" s="1" t="n">
+        <v>3538.70497</v>
+      </c>
+    </row>
+    <row r="6549">
+      <c r="A6549" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B6549" s="1" t="n">
+        <v>3530.49305</v>
+      </c>
+    </row>
+    <row r="6550">
+      <c r="A6550" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B6550" s="1" t="n">
+        <v>3519.36623</v>
+      </c>
+    </row>
+    <row r="6551">
+      <c r="A6551" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B6551" s="1" t="n">
+        <v>3506.73687</v>
+      </c>
+    </row>
+    <row r="6552">
+      <c r="A6552" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B6552" s="1" t="n">
+        <v>3530.1313</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/tasa_eur.xlsx
+++ b/data/tasa_eur.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6552"/>
+  <dimension ref="A1:B6555"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65941,6 +65941,36 @@
         <v>3530.1313</v>
       </c>
     </row>
+    <row r="6553">
+      <c r="A6553" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B6553" s="1" t="n">
+        <v>3535.22163</v>
+      </c>
+    </row>
+    <row r="6554">
+      <c r="A6554" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B6554" s="1" t="n">
+        <v>3553.17173</v>
+      </c>
+    </row>
+    <row r="6555">
+      <c r="A6555" t="inlineStr">
+        <is>
+          <t>2026-11-01</t>
+        </is>
+      </c>
+      <c r="B6555" s="1" t="n">
+        <v>3553.17173</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
